--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-15.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-15.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2439,27 +2439,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VENEZUELA 1</t>
+          <t>PERU 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Puerto Cabello x Rayo Zuliano</t>
+          <t>Alianza Lima x UTC Cajamarca</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Alianza Lima</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rayo Zuliano</t>
+          <t>UTC Cajamarca</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2478,20 +2478,20 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="K26" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="L26" t="n">
-        <v>21.28</v>
+        <v>16.67</v>
       </c>
       <c r="M26" t="n">
         <v>100</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2518,37 +2518,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PERU 1</t>
+          <t>VENEZUELA 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Alianza Lima x UTC Cajamarca</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Alianza Lima</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>UTC Cajamarca</t>
-        </is>
-      </c>
+          <t>Puerto Cabello x Rayo Zuliano</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Away)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2557,37 +2549,43 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="K27" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="L27" t="n">
-        <v>16.67</v>
+        <v>8</v>
       </c>
       <c r="M27" t="n">
         <v>100</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2597,17 +2595,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VENEZUELA 1</t>
+          <t>ITALY CUP</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Puerto Cabello x Rayo Zuliano</t>
+          <t>Udinese x Padova</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -2628,20 +2626,20 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="K28" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="L28" t="n">
-        <v>8</v>
+        <v>9.52</v>
       </c>
       <c r="M28" t="n">
         <v>100</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2655,89 +2653,12 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="T28" t="b">
+        <v>9.19</v>
+      </c>
+      <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="inlineStr">
-        <is>
-          <t>LIQUIDADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>ITALY CUP</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Udinese x Padova</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Match Odds (Away)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="L29" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="M29" t="n">
-        <v>100</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>1x0</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="n">
-        <v>9.19</v>
-      </c>
-      <c r="T29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U29" t="inlineStr">
         <is>
           <t>LIQUIDADO</t>
         </is>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-15.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +623,8 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -692,6 +704,8 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -771,6 +785,8 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -850,6 +866,8 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -929,6 +947,8 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1008,6 +1028,8 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1087,6 +1109,8 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1166,6 +1190,8 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1245,6 +1271,8 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1324,6 +1352,8 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1403,6 +1433,8 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1482,6 +1514,8 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1561,6 +1595,8 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1640,6 +1676,8 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1757,8 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1798,6 +1838,8 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1877,6 +1919,8 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1886,37 +1930,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CZECH 1</t>
+          <t>ITALY CUP</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Plzen x Zlin</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Plzen</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Zlin</t>
-        </is>
-      </c>
+          <t>Udinese x Padova</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Away)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1925,37 +1961,45 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="L19" t="n">
-        <v>18.52</v>
+        <v>9.52</v>
       </c>
       <c r="M19" t="n">
         <v>100</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1970,32 +2014,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NETHERLANDS 1</t>
+          <t>CZECH 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Excelsior x PSV</t>
+          <t>Plzen x Zlin</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Plzen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Zlin</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2004,20 +2048,20 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="K20" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="L20" t="n">
-        <v>15.15</v>
+        <v>18.52</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2035,6 +2079,8 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2049,32 +2095,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SOUTH AFRICA 1</t>
+          <t>NETHERLANDS 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Milford x Kruger United FC</t>
+          <t>Excelsior x PSV</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kruger United FC</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Over 4.5 FT</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2083,20 +2129,20 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="K21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="L21" t="n">
-        <v>5.26</v>
+        <v>15.15</v>
       </c>
       <c r="M21" t="n">
         <v>100</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2114,6 +2160,8 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2123,37 +2171,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BELGIUM 1</t>
+          <t>SOUTH AFRICA 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Oud-Heverlee Leuven x Club Brugge</t>
+          <t>Milford x Kruger United FC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oud-Heverlee Leuven</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Kruger United FC</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Over 4.5 FT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2162,20 +2210,20 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="K22" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="L22" t="n">
-        <v>16.13</v>
+        <v>5.26</v>
       </c>
       <c r="M22" t="n">
         <v>100</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0x3</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2193,6 +2241,8 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2202,37 +2252,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>BELGIUM 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Rio Ave x Porto</t>
+          <t>Oud-Heverlee Leuven x Club Brugge</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Oud-Heverlee Leuven</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2241,20 +2291,20 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="K23" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="L23" t="n">
-        <v>23.81</v>
+        <v>16.13</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0x3</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2272,6 +2322,8 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2281,37 +2333,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ARGENTINA 1</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Estudiantes x Gimnasia La Plata</t>
+          <t>Atletico GO x Vila Nova FC</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Vila Nova FC</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Over 4.5 FT</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2320,37 +2372,47 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="K24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>5.41</v>
+        <v>8.33</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4x0</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>8.039999999999999</v>
+      </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="W24" t="n">
+        <v>8.039999999999999</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2360,37 +2422,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MEXICO 1</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Atlante x Toluca</t>
+          <t>Rio Ave x Porto</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atlante</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2399,20 +2461,20 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="K25" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="L25" t="n">
-        <v>19.23</v>
+        <v>23.81</v>
       </c>
       <c r="M25" t="n">
         <v>100</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2430,6 +2492,8 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2439,37 +2503,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PERU 1</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Alianza Lima x UTC Cajamarca</t>
+          <t>Estudiantes x Gimnasia La Plata</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alianza Lima</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UTC Cajamarca</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Over 4.5 FT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2478,20 +2542,20 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>7</v>
+        <v>19.5</v>
       </c>
       <c r="K26" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="L26" t="n">
-        <v>16.67</v>
+        <v>5.41</v>
       </c>
       <c r="M26" t="n">
         <v>100</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>4x0</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2509,6 +2573,8 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2518,29 +2584,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>VENEZUELA 1</t>
+          <t>ARGENTINA 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Puerto Cabello x Rayo Zuliano</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+          <t>Godoy Cruz x Deportivo Maipu</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Deportivo Maipu</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2549,20 +2623,20 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="K27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>8</v>
+        <v>10.81</v>
       </c>
       <c r="M27" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2574,17 +2648,21 @@
         <v>1</v>
       </c>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
       <c r="S27" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>LIQUIDADO</t>
-        </is>
+        <v>10.43</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="n">
+        <v>0.0522</v>
+      </c>
+      <c r="W27" t="n">
+        <v>10.43</v>
       </c>
     </row>
     <row r="28">
@@ -2595,29 +2673,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ITALY CUP</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Udinese x Padova</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+          <t>Belgrano x Ind. Rivadavia</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Belgrano</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ind. Rivadavia</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2626,20 +2712,20 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>11.5</v>
+        <v>24</v>
       </c>
       <c r="K28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>9.52</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2651,18 +2737,263 @@
         <v>1</v>
       </c>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
       <c r="S28" t="n">
-        <v>9.19</v>
-      </c>
-      <c r="T28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="W28" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MEXICO 1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Atlante x Toluca</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Toluca</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Match Odds (Home)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="M29" t="n">
+        <v>100</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>VENEZUELA 1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Puerto Cabello x Rayo Zuliano</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Match Odds (Away)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L30" t="n">
+        <v>8</v>
+      </c>
+      <c r="M30" t="n">
+        <v>100</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2x0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
         <v>1</v>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr">
         <is>
           <t>LIQUIDADO</t>
         </is>
       </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PERU 1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Alianza Lima x UTC Cajamarca</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Alianza Lima</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>UTC Cajamarca</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Match Odds (Draw)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L31" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="M31" t="n">
+        <v>100</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>1x0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-15.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-15.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -686,12 +686,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -767,12 +767,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4x2</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -929,12 +929,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3x4</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4x3</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>5x0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2223,12 +2223,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0x3</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>4x0</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2814,12 +2814,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2974,12 +2974,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-15.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-15.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -686,12 +686,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -767,12 +767,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4x2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -929,12 +929,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>3x4</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>4x3</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>5x0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2223,12 +2223,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0x3</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>4x0</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2814,12 +2814,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2974,12 +2974,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
